--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3778,6 +3778,1564 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46147.63775737269</v>
+      </c>
+      <c r="F65" t="n">
+        <v>76080</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H65" t="n">
+        <v>38</v>
+      </c>
+      <c r="I65" t="n">
+        <v>12</v>
+      </c>
+      <c r="J65" t="n">
+        <v>10</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>49</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>46146.78474440972</v>
+      </c>
+      <c r="F66" t="n">
+        <v>79555</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H66" t="n">
+        <v>62</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>10</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>47</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46146.20173063657</v>
+      </c>
+      <c r="F67" t="n">
+        <v>78707</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H67" t="n">
+        <v>70</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>29</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>45</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46145.79895810185</v>
+      </c>
+      <c r="F68" t="n">
+        <v>60699</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H68" t="n">
+        <v>57</v>
+      </c>
+      <c r="I68" t="n">
+        <v>11</v>
+      </c>
+      <c r="J68" t="n">
+        <v>28</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>44</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>46145.79860146991</v>
+      </c>
+      <c r="F69" t="n">
+        <v>78075</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H69" t="n">
+        <v>93</v>
+      </c>
+      <c r="I69" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>23</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>42</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>46142.78272005787</v>
+      </c>
+      <c r="F70" t="n">
+        <v>72270</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H70" t="n">
+        <v>56</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" t="n">
+        <v>14</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>40</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46142.28542734954</v>
+      </c>
+      <c r="F71" t="n">
+        <v>74720</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" t="n">
+        <v>6</v>
+      </c>
+      <c r="J71" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>39</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>46141.80448515046</v>
+      </c>
+      <c r="F72" t="n">
+        <v>71103</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H72" t="n">
+        <v>42</v>
+      </c>
+      <c r="I72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J72" t="n">
+        <v>19</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>38</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46141.23215089121</v>
+      </c>
+      <c r="F73" t="n">
+        <v>73911</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H73" t="n">
+        <v>36</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7</v>
+      </c>
+      <c r="J73" t="n">
+        <v>33</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>37</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46141.23183086806</v>
+      </c>
+      <c r="F74" t="n">
+        <v>74802</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H74" t="n">
+        <v>71</v>
+      </c>
+      <c r="I74" t="n">
+        <v>12</v>
+      </c>
+      <c r="J74" t="n">
+        <v>24</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>35</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46140.25642711805</v>
+      </c>
+      <c r="F75" t="n">
+        <v>66592</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H75" t="n">
+        <v>78</v>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>33</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>46139.95176119213</v>
+      </c>
+      <c r="F76" t="n">
+        <v>73894</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H76" t="n">
+        <v>69</v>
+      </c>
+      <c r="I76" t="n">
+        <v>23</v>
+      </c>
+      <c r="J76" t="n">
+        <v>25</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>31</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>46137.7763449074</v>
+      </c>
+      <c r="F77" t="n">
+        <v>72532</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H77" t="n">
+        <v>21</v>
+      </c>
+      <c r="I77" t="n">
+        <v>8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>29</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46137.77484413194</v>
+      </c>
+      <c r="F78" t="n">
+        <v>78436</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H78" t="n">
+        <v>19</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>14</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>28</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>46137.26448283565</v>
+      </c>
+      <c r="F79" t="n">
+        <v>69549</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H79" t="n">
+        <v>117</v>
+      </c>
+      <c r="I79" t="n">
+        <v>29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>30</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>27</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46137.26421554398</v>
+      </c>
+      <c r="F80" t="n">
+        <v>69642</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H80" t="n">
+        <v>79</v>
+      </c>
+      <c r="I80" t="n">
+        <v>14</v>
+      </c>
+      <c r="J80" t="n">
+        <v>27</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>26</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>46136.76209146991</v>
+      </c>
+      <c r="F81" t="n">
+        <v>69981</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H81" t="n">
+        <v>41</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J81" t="n">
+        <v>17</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>46136.61478958333</v>
+      </c>
+      <c r="F82" t="n">
+        <v>71566</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H82" t="n">
+        <v>22</v>
+      </c>
+      <c r="I82" t="n">
+        <v>10</v>
+      </c>
+      <c r="J82" t="n">
+        <v>9</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>24</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46136.26324667824</v>
+      </c>
+      <c r="F83" t="n">
+        <v>52882</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H83" t="n">
+        <v>40</v>
+      </c>
+      <c r="I83" t="n">
+        <v>10</v>
+      </c>
+      <c r="J83" t="n">
+        <v>11</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>23</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>46136.2630162037</v>
+      </c>
+      <c r="F84" t="n">
+        <v>66449</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H84" t="n">
+        <v>44</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>22</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46135.94104097222</v>
+      </c>
+      <c r="F85" t="n">
+        <v>70515</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H85" t="n">
+        <v>32</v>
+      </c>
+      <c r="I85" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" t="n">
+        <v>9</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>46135.62556388889</v>
+      </c>
+      <c r="F86" t="n">
+        <v>69043</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H86" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" t="n">
+        <v>18</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>18</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>46134.61827450232</v>
+      </c>
+      <c r="F87" t="n">
+        <v>68968</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H87" t="n">
+        <v>48</v>
+      </c>
+      <c r="I87" t="n">
+        <v>18</v>
+      </c>
+      <c r="J87" t="n">
+        <v>13</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>17</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46132.26061805555</v>
+      </c>
+      <c r="F88" t="n">
+        <v>67135</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H88" t="n">
+        <v>34</v>
+      </c>
+      <c r="I88" t="n">
+        <v>18</v>
+      </c>
+      <c r="J88" t="n">
+        <v>21</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>15</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>46130.78555181713</v>
+      </c>
+      <c r="F89" t="n">
+        <v>65058</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H89" t="n">
+        <v>53</v>
+      </c>
+      <c r="I89" t="n">
+        <v>19</v>
+      </c>
+      <c r="J89" t="n">
+        <v>14</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>46130.64340679398</v>
+      </c>
+      <c r="F90" t="n">
+        <v>65621</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H90" t="n">
+        <v>32</v>
+      </c>
+      <c r="I90" t="n">
+        <v>16</v>
+      </c>
+      <c r="J90" t="n">
+        <v>9</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>46129.67677141204</v>
+      </c>
+      <c r="F91" t="n">
+        <v>64677</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H91" t="n">
+        <v>114</v>
+      </c>
+      <c r="I91" t="n">
+        <v>10</v>
+      </c>
+      <c r="J91" t="n">
+        <v>32</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>46128.61458815973</v>
+      </c>
+      <c r="F92" t="n">
+        <v>64116</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H92" t="n">
+        <v>35</v>
+      </c>
+      <c r="I92" t="n">
+        <v>38</v>
+      </c>
+      <c r="J92" t="n">
+        <v>39</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>46127.94790601852</v>
+      </c>
+      <c r="F93" t="n">
+        <v>62604</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H93" t="n">
+        <v>90</v>
+      </c>
+      <c r="I93" t="n">
+        <v>10</v>
+      </c>
+      <c r="J93" t="n">
+        <v>18</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:19:47</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>46126.72113649306</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H94" t="n">
+        <v>83</v>
+      </c>
+      <c r="I94" t="n">
+        <v>32</v>
+      </c>
+      <c r="J94" t="n">
+        <v>17</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5336,6 +5336,1252 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>37</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>46148.30348109954</v>
+      </c>
+      <c r="F95" t="n">
+        <v>79493</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H95" t="n">
+        <v>68</v>
+      </c>
+      <c r="I95" t="n">
+        <v>17</v>
+      </c>
+      <c r="J95" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>36</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>46148.30319927083</v>
+      </c>
+      <c r="F96" t="n">
+        <v>805800</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H96" t="n">
+        <v>79</v>
+      </c>
+      <c r="I96" t="n">
+        <v>12</v>
+      </c>
+      <c r="J96" t="n">
+        <v>22</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>34</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>46147.63828584491</v>
+      </c>
+      <c r="F97" t="n">
+        <v>80119</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H97" t="n">
+        <v>81</v>
+      </c>
+      <c r="I97" t="n">
+        <v>7</v>
+      </c>
+      <c r="J97" t="n">
+        <v>10</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>33</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>46146.78476855324</v>
+      </c>
+      <c r="F98" t="n">
+        <v>78803</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H98" t="n">
+        <v>357</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>3</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>31</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>46146.20224267361</v>
+      </c>
+      <c r="F99" t="n">
+        <v>78954</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H99" t="n">
+        <v>55</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>16</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>30</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>46141.80501840277</v>
+      </c>
+      <c r="F100" t="n">
+        <v>75347</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H100" t="n">
+        <v>57</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>15</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>29</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>46141.23302908565</v>
+      </c>
+      <c r="F101" t="n">
+        <v>74532</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H101" t="n">
+        <v>186</v>
+      </c>
+      <c r="I101" t="n">
+        <v>12</v>
+      </c>
+      <c r="J101" t="n">
+        <v>11</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>28</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>46141.2325318287</v>
+      </c>
+      <c r="F102" t="n">
+        <v>74143</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H102" t="n">
+        <v>475</v>
+      </c>
+      <c r="I102" t="n">
+        <v>18</v>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>26</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>46140.25598101852</v>
+      </c>
+      <c r="F103" t="n">
+        <v>73932</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H103" t="n">
+        <v>114</v>
+      </c>
+      <c r="I103" t="n">
+        <v>33</v>
+      </c>
+      <c r="J103" t="n">
+        <v>21</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>25</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>46139.95215228009</v>
+      </c>
+      <c r="F104" t="n">
+        <v>65787</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H104" t="n">
+        <v>60</v>
+      </c>
+      <c r="I104" t="n">
+        <v>29</v>
+      </c>
+      <c r="J104" t="n">
+        <v>29</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>23</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>46137.7768158912</v>
+      </c>
+      <c r="F105" t="n">
+        <v>70123</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H105" t="n">
+        <v>16</v>
+      </c>
+      <c r="I105" t="n">
+        <v>4</v>
+      </c>
+      <c r="J105" t="n">
+        <v>19</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>21</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>46137.77520709491</v>
+      </c>
+      <c r="F106" t="n">
+        <v>72357</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H106" t="n">
+        <v>21</v>
+      </c>
+      <c r="I106" t="n">
+        <v>8</v>
+      </c>
+      <c r="J106" t="n">
+        <v>11</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>46137.2660540162</v>
+      </c>
+      <c r="F107" t="n">
+        <v>70588</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H107" t="n">
+        <v>66</v>
+      </c>
+      <c r="I107" t="n">
+        <v>7</v>
+      </c>
+      <c r="J107" t="n">
+        <v>14</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>19</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>46137.26546369213</v>
+      </c>
+      <c r="F108" t="n">
+        <v>69663</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H108" t="n">
+        <v>86</v>
+      </c>
+      <c r="I108" t="n">
+        <v>11</v>
+      </c>
+      <c r="J108" t="n">
+        <v>31</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>17</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>46136.76248579861</v>
+      </c>
+      <c r="F109" t="n">
+        <v>69538</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H109" t="n">
+        <v>26</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" t="n">
+        <v>14</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>16</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>46136.61543568287</v>
+      </c>
+      <c r="F110" t="n">
+        <v>71178</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H110" t="n">
+        <v>29</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6</v>
+      </c>
+      <c r="J110" t="n">
+        <v>10</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>15</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>46135.94129672454</v>
+      </c>
+      <c r="F111" t="n">
+        <v>70669</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H111" t="n">
+        <v>46</v>
+      </c>
+      <c r="I111" t="n">
+        <v>4</v>
+      </c>
+      <c r="J111" t="n">
+        <v>15</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>13</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>46135.62638387732</v>
+      </c>
+      <c r="F112" t="n">
+        <v>70159</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H112" t="n">
+        <v>22</v>
+      </c>
+      <c r="I112" t="n">
+        <v>8</v>
+      </c>
+      <c r="J112" t="n">
+        <v>16</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>46135.28301226852</v>
+      </c>
+      <c r="F113" t="n">
+        <v>69656</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H113" t="n">
+        <v>63</v>
+      </c>
+      <c r="I113" t="n">
+        <v>12</v>
+      </c>
+      <c r="J113" t="n">
+        <v>21</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>9</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46134.61890821759</v>
+      </c>
+      <c r="F114" t="n">
+        <v>69397</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H114" t="n">
+        <v>81</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>11</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>7</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>46132.80492002315</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H115" t="n">
+        <v>121</v>
+      </c>
+      <c r="I115" t="n">
+        <v>25</v>
+      </c>
+      <c r="J115" t="n">
+        <v>20</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>46130.23395628472</v>
+      </c>
+      <c r="F116" t="n">
+        <v>54925</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H116" t="n">
+        <v>74</v>
+      </c>
+      <c r="I116" t="n">
+        <v>23</v>
+      </c>
+      <c r="J116" t="n">
+        <v>21</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>4</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>46129.67848822917</v>
+      </c>
+      <c r="F117" t="n">
+        <v>64273</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H117" t="n">
+        <v>21</v>
+      </c>
+      <c r="I117" t="n">
+        <v>16</v>
+      </c>
+      <c r="J117" t="n">
+        <v>12</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:21:10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>46126.80844768519</v>
+      </c>
+      <c r="F118" t="n">
+        <v>62920</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H118" t="n">
+        <v>86</v>
+      </c>
+      <c r="I118" t="n">
+        <v>14</v>
+      </c>
+      <c r="J118" t="n">
+        <v>27</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6582,6 +6582,990 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>30</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46147.93847060185</v>
+      </c>
+      <c r="F119" t="n">
+        <v>80887</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H119" t="n">
+        <v>92</v>
+      </c>
+      <c r="I119" t="n">
+        <v>14</v>
+      </c>
+      <c r="J119" t="n">
+        <v>24</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>28</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>46147.63876871527</v>
+      </c>
+      <c r="F120" t="n">
+        <v>75709</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H120" t="n">
+        <v>91</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>19</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>26</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>46145.79992392361</v>
+      </c>
+      <c r="F121" t="n">
+        <v>72083</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H121" t="n">
+        <v>114</v>
+      </c>
+      <c r="I121" t="n">
+        <v>14</v>
+      </c>
+      <c r="J121" t="n">
+        <v>20</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>46145.79946319445</v>
+      </c>
+      <c r="F122" t="n">
+        <v>59499</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H122" t="n">
+        <v>113</v>
+      </c>
+      <c r="I122" t="n">
+        <v>12</v>
+      </c>
+      <c r="J122" t="n">
+        <v>18</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>24</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>46142.78314910879</v>
+      </c>
+      <c r="F123" t="n">
+        <v>75113</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H123" t="n">
+        <v>44</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5</v>
+      </c>
+      <c r="J123" t="n">
+        <v>11</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>23</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>46142.28598116899</v>
+      </c>
+      <c r="F124" t="n">
+        <v>75615</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H124" t="n">
+        <v>43</v>
+      </c>
+      <c r="I124" t="n">
+        <v>22</v>
+      </c>
+      <c r="J124" t="n">
+        <v>13</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>22</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>46141.80530104167</v>
+      </c>
+      <c r="F125" t="n">
+        <v>74915</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H125" t="n">
+        <v>93</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>46139.95272364583</v>
+      </c>
+      <c r="F126" t="n">
+        <v>66592</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H126" t="n">
+        <v>74</v>
+      </c>
+      <c r="I126" t="n">
+        <v>16</v>
+      </c>
+      <c r="J126" t="n">
+        <v>28</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>19</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>46139.63956172454</v>
+      </c>
+      <c r="F127" t="n">
+        <v>67778</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H127" t="n">
+        <v>52</v>
+      </c>
+      <c r="I127" t="n">
+        <v>13</v>
+      </c>
+      <c r="J127" t="n">
+        <v>6</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>17</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46137.77562673611</v>
+      </c>
+      <c r="F128" t="n">
+        <v>69933</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H128" t="n">
+        <v>12</v>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>15</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46136.89953047454</v>
+      </c>
+      <c r="F129" t="n">
+        <v>70278</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H129" t="n">
+        <v>62</v>
+      </c>
+      <c r="I129" t="n">
+        <v>4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>24</v>
+      </c>
+      <c r="K129" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>14</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>46136.61596099537</v>
+      </c>
+      <c r="F130" t="n">
+        <v>71688</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H130" t="n">
+        <v>23</v>
+      </c>
+      <c r="I130" t="n">
+        <v>10</v>
+      </c>
+      <c r="J130" t="n">
+        <v>15</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>46135.62717079861</v>
+      </c>
+      <c r="F131" t="n">
+        <v>69919</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H131" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" t="n">
+        <v>10</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>46134.94094375</v>
+      </c>
+      <c r="F132" t="n">
+        <v>44033</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H132" t="n">
+        <v>68</v>
+      </c>
+      <c r="I132" t="n">
+        <v>10</v>
+      </c>
+      <c r="J132" t="n">
+        <v>13</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>46129.67888642361</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H133" t="n">
+        <v>92</v>
+      </c>
+      <c r="I133" t="n">
+        <v>20</v>
+      </c>
+      <c r="J133" t="n">
+        <v>16</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>8</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>46128.94660697917</v>
+      </c>
+      <c r="F134" t="n">
+        <v>56574</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H134" t="n">
+        <v>39</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>46127.64516608796</v>
+      </c>
+      <c r="F135" t="n">
+        <v>60451</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H135" t="n">
+        <v>74</v>
+      </c>
+      <c r="I135" t="n">
+        <v>21</v>
+      </c>
+      <c r="J135" t="n">
+        <v>11</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>4</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>46126.72178568287</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H136" t="n">
+        <v>103</v>
+      </c>
+      <c r="I136" t="n">
+        <v>21</v>
+      </c>
+      <c r="J136" t="n">
+        <v>15</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:22:31</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>46122.95219961806</v>
+      </c>
+      <c r="F137" t="n">
+        <v>57260</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H137" t="n">
+        <v>10</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>6</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7566,6 +7566,990 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>28</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>46148.3041522338</v>
+      </c>
+      <c r="F138" t="n">
+        <v>81011</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H138" t="n">
+        <v>74</v>
+      </c>
+      <c r="I138" t="n">
+        <v>14</v>
+      </c>
+      <c r="J138" t="n">
+        <v>7</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>27</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>46148.30389984954</v>
+      </c>
+      <c r="F139" t="n">
+        <v>80892</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H139" t="n">
+        <v>115</v>
+      </c>
+      <c r="I139" t="n">
+        <v>26</v>
+      </c>
+      <c r="J139" t="n">
+        <v>18</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>26</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>46147.93871223379</v>
+      </c>
+      <c r="F140" t="n">
+        <v>80886</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H140" t="n">
+        <v>68</v>
+      </c>
+      <c r="I140" t="n">
+        <v>11</v>
+      </c>
+      <c r="J140" t="n">
+        <v>20</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>24</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>46147.63924563657</v>
+      </c>
+      <c r="F141" t="n">
+        <v>80756</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H141" t="n">
+        <v>94</v>
+      </c>
+      <c r="I141" t="n">
+        <v>11</v>
+      </c>
+      <c r="J141" t="n">
+        <v>18</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>23</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>46141.80631006944</v>
+      </c>
+      <c r="F142" t="n">
+        <v>75061</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H142" t="n">
+        <v>84</v>
+      </c>
+      <c r="I142" t="n">
+        <v>10</v>
+      </c>
+      <c r="J142" t="n">
+        <v>22</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>22</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>46139.9529977662</v>
+      </c>
+      <c r="F143" t="n">
+        <v>73932</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H143" t="n">
+        <v>68</v>
+      </c>
+      <c r="I143" t="n">
+        <v>12</v>
+      </c>
+      <c r="J143" t="n">
+        <v>25</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>3</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>20</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>46137.77595008102</v>
+      </c>
+      <c r="F144" t="n">
+        <v>71527</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H144" t="n">
+        <v>27</v>
+      </c>
+      <c r="I144" t="n">
+        <v>6</v>
+      </c>
+      <c r="J144" t="n">
+        <v>14</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>18</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>46136.89997878472</v>
+      </c>
+      <c r="F145" t="n">
+        <v>71859</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H145" t="n">
+        <v>53</v>
+      </c>
+      <c r="I145" t="n">
+        <v>9</v>
+      </c>
+      <c r="J145" t="n">
+        <v>21</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>17</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>46136.61634829861</v>
+      </c>
+      <c r="F146" t="n">
+        <v>71691</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H146" t="n">
+        <v>31</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>12</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>15</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>46135.62750142361</v>
+      </c>
+      <c r="F147" t="n">
+        <v>70603</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H147" t="n">
+        <v>20</v>
+      </c>
+      <c r="I147" t="n">
+        <v>15</v>
+      </c>
+      <c r="J147" t="n">
+        <v>10</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>13</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>46135.28353399305</v>
+      </c>
+      <c r="F148" t="n">
+        <v>69893</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H148" t="n">
+        <v>38</v>
+      </c>
+      <c r="I148" t="n">
+        <v>8</v>
+      </c>
+      <c r="J148" t="n">
+        <v>17</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>12</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>46134.94126489583</v>
+      </c>
+      <c r="F149" t="n">
+        <v>58618</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H149" t="n">
+        <v>62</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>16</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>46132.80535023148</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H150" t="n">
+        <v>181</v>
+      </c>
+      <c r="I150" t="n">
+        <v>19</v>
+      </c>
+      <c r="J150" t="n">
+        <v>16</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>46130.78615605324</v>
+      </c>
+      <c r="F151" t="n">
+        <v>65602</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H151" t="n">
+        <v>44</v>
+      </c>
+      <c r="I151" t="n">
+        <v>25</v>
+      </c>
+      <c r="J151" t="n">
+        <v>9</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>6</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>46130.64379594907</v>
+      </c>
+      <c r="F152" t="n">
+        <v>65685</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H152" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>5</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>46130.23432924769</v>
+      </c>
+      <c r="F153" t="n">
+        <v>55269</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H153" t="n">
+        <v>78</v>
+      </c>
+      <c r="I153" t="n">
+        <v>18</v>
+      </c>
+      <c r="J153" t="n">
+        <v>22</v>
+      </c>
+      <c r="K153" t="n">
+        <v>2</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>46129.67915755787</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H154" t="n">
+        <v>27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>4</v>
+      </c>
+      <c r="J154" t="n">
+        <v>7</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>46128.94689100694</v>
+      </c>
+      <c r="F155" t="n">
+        <v>56207</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H155" t="n">
+        <v>37</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" t="n">
+        <v>9</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:23:53</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46128.87328869213</v>
+      </c>
+      <c r="F156" t="n">
+        <v>64116</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H156" t="n">
+        <v>13</v>
+      </c>
+      <c r="I156" t="n">
+        <v>10</v>
+      </c>
+      <c r="J156" t="n">
+        <v>19</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:R186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,26 @@
           <t>Capturador</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OP250A-P1-CANT-MAX-SED - CANTIDAD MÁXIMA DE SEDIMENTOS EN CIGUEÑAL</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OP250A-P1-TAMÑ-MAX-PART-CONT - TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OP250-P2-CANT-MX-SED - CANTIDAD MAXIMA DE SEDIMENTOS</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OP-250A-P2-TAMÑ-MAX-PART-CONT - PALLET 2 TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -555,6 +575,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -607,6 +631,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,6 +687,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -711,6 +743,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -763,6 +799,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -815,6 +855,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -867,6 +911,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -919,6 +967,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -971,6 +1023,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1023,6 +1079,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1075,6 +1135,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1127,6 +1191,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1179,6 +1247,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1231,6 +1303,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1283,6 +1359,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1335,6 +1415,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1387,6 +1471,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1439,6 +1527,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1491,6 +1583,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1543,6 +1639,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1595,6 +1695,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1647,6 +1751,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1699,6 +1807,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1751,6 +1863,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1803,6 +1919,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1855,6 +1975,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1907,6 +2031,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1959,6 +2087,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2011,6 +2143,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2063,6 +2199,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2115,6 +2255,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2167,6 +2311,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2219,6 +2367,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2271,6 +2423,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2323,6 +2479,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2375,6 +2535,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2427,6 +2591,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2479,6 +2647,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2531,6 +2703,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2583,6 +2759,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2635,6 +2815,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2687,6 +2871,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2739,6 +2927,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2791,6 +2983,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2841,6 +3037,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2893,6 +3093,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2945,6 +3149,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2997,6 +3205,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3049,6 +3261,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3101,6 +3317,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3153,6 +3373,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3205,6 +3429,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3257,6 +3485,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3309,6 +3541,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3361,6 +3597,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3413,6 +3653,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3465,6 +3709,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3517,6 +3765,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3569,6 +3821,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3621,6 +3877,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3673,6 +3933,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3725,6 +3989,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3777,6 +4045,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3829,6 +4101,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3881,6 +4157,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3933,6 +4213,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3985,6 +4269,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4037,6 +4325,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4089,6 +4381,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4141,6 +4437,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4193,6 +4493,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4245,6 +4549,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4297,6 +4605,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4349,6 +4661,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4401,6 +4717,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4453,6 +4773,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4505,6 +4829,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4557,6 +4885,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4609,6 +4941,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4661,6 +4997,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4713,6 +5053,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4765,6 +5109,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4817,6 +5165,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4869,6 +5221,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4921,6 +5277,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4973,6 +5333,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5025,6 +5389,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5077,6 +5445,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5129,6 +5501,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5181,6 +5557,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5233,6 +5613,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5285,6 +5669,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5335,6 +5723,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5387,6 +5779,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5439,6 +5835,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5491,6 +5891,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5543,6 +5947,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5595,6 +6003,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5647,6 +6059,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5699,6 +6115,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5751,6 +6171,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5803,6 +6227,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5855,6 +6283,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5907,6 +6339,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5959,6 +6395,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6011,6 +6451,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6063,6 +6507,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6115,6 +6563,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6167,6 +6619,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6219,6 +6675,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6271,6 +6731,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6323,6 +6787,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6375,6 +6843,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6425,6 +6897,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6477,6 +6953,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6529,6 +7009,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6581,6 +7065,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6633,6 +7121,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6685,6 +7177,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6737,6 +7233,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6789,6 +7289,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6841,6 +7345,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6893,6 +7401,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6945,6 +7457,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6997,6 +7513,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7049,6 +7569,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7101,6 +7625,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7153,6 +7681,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7205,6 +7737,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7257,6 +7793,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7309,6 +7849,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7359,6 +7903,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7411,6 +7959,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7463,6 +8015,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7513,6 +8069,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7565,6 +8125,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7617,6 +8181,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7669,6 +8237,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7721,6 +8293,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7773,6 +8349,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7825,6 +8405,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7877,6 +8461,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7929,6 +8517,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7981,6 +8573,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8033,6 +8629,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8085,6 +8685,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8137,6 +8741,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8189,6 +8797,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8239,6 +8851,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8291,6 +8907,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8343,6 +8963,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8395,6 +9019,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8445,6 +9073,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8497,6 +9129,10 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8549,6 +9185,1434 @@
           <t>Oscar Saucedo Mendieta</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>629</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>46147.93938163194</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>628</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>46147.30529413195</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>626</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>46142.28737384259</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.276</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>625</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46141.80884197917</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.438</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>624</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46141.80829452546</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.502</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>623</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>46141.80793359954</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>622</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>46141.23464876157</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.391</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>621</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>46139.95437916667</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.528</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>620</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>46138.80580034723</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>619</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>46138.80544158565</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>618</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>46137.7788162037</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>617</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>46137.77851038195</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>615</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>46136.76072306713</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.591</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>614</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>46136.61789722222</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.579</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>613</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>46135.93963109954</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>611</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46135.62895987269</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>610</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>46134.93833425926</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.586</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>608</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>46134.62196600695</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.511</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>607</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>46133.96499421296</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.582</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>605</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>46133.64347612268</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0.505</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>604</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>46132.80430100695</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.505</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>603</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>46132.61887288195</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.582</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>602</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>46130.78241103009</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.397</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>600</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>46130.64431554398</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.521</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>599</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>46130.23244186342</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P181" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.796</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>597</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>46129.68032268518</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.327</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>596</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>46128.6166440625</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>595</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>46127.9500162037</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.554</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>593</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>46127.64626924769</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.593</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:25:14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>592</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>46126.80897890047</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R186"/>
+  <dimension ref="A1:V216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,26 @@
           <t>OP-250A-P2-TAMÑ-MAX-PART-CONT - PALLET 2 TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OP250B-P1-CANT-MAX-SED - CANTIDAD MÁXIMA DE SEDIMENTOS EN CIGUEÑAL</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OP250B-P1-TAMÑ-MAX-PART-CONT - TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OP250B-P2-CANT-MAX-SED - CANTIDAD MÁXIMA DE SEDIMENTOS EN CIGUEÑAL</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OP250B-P2-TAMÑ-MAX-PART-CONT - TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -579,6 +599,10 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,6 +659,10 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,6 +719,10 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,6 +779,10 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -803,6 +839,10 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -859,6 +899,10 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -915,6 +959,10 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -971,6 +1019,10 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1027,6 +1079,10 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1083,6 +1139,10 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1139,6 +1199,10 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1195,6 +1259,10 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1251,6 +1319,10 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1307,6 +1379,10 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1363,6 +1439,10 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1419,6 +1499,10 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1475,6 +1559,10 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1531,6 +1619,10 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1587,6 +1679,10 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1643,6 +1739,10 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1699,6 +1799,10 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1755,6 +1859,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1811,6 +1919,10 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1867,6 +1979,10 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1923,6 +2039,10 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1979,6 +2099,10 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2035,6 +2159,10 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2091,6 +2219,10 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2147,6 +2279,10 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2203,6 +2339,10 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2259,6 +2399,10 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2315,6 +2459,10 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2371,6 +2519,10 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2427,6 +2579,10 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2483,6 +2639,10 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2539,6 +2699,10 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2595,6 +2759,10 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2651,6 +2819,10 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2707,6 +2879,10 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2763,6 +2939,10 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2819,6 +2999,10 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2875,6 +3059,10 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2931,6 +3119,10 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2987,6 +3179,10 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3041,6 +3237,10 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3097,6 +3297,10 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3153,6 +3357,10 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3209,6 +3417,10 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3265,6 +3477,10 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3321,6 +3537,10 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3377,6 +3597,10 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3433,6 +3657,10 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3489,6 +3717,10 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3545,6 +3777,10 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3601,6 +3837,10 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3657,6 +3897,10 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3713,6 +3957,10 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3769,6 +4017,10 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3825,6 +4077,10 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3881,6 +4137,10 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3937,6 +4197,10 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3993,6 +4257,10 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4049,6 +4317,10 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4105,6 +4377,10 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4161,6 +4437,10 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4217,6 +4497,10 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4273,6 +4557,10 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4329,6 +4617,10 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4385,6 +4677,10 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4441,6 +4737,10 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4497,6 +4797,10 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4553,6 +4857,10 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4609,6 +4917,10 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4665,6 +4977,10 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4721,6 +5037,10 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4777,6 +5097,10 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4833,6 +5157,10 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4889,6 +5217,10 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4945,6 +5277,10 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5001,6 +5337,10 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5057,6 +5397,10 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5113,6 +5457,10 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5169,6 +5517,10 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5225,6 +5577,10 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5281,6 +5637,10 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5337,6 +5697,10 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5393,6 +5757,10 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5449,6 +5817,10 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5505,6 +5877,10 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5561,6 +5937,10 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5617,6 +5997,10 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5673,6 +6057,10 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5727,6 +6115,10 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5783,6 +6175,10 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5839,6 +6235,10 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5895,6 +6295,10 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5951,6 +6355,10 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6007,6 +6415,10 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6063,6 +6475,10 @@
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6119,6 +6535,10 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6175,6 +6595,10 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6231,6 +6655,10 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6287,6 +6715,10 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6343,6 +6775,10 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6399,6 +6835,10 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6455,6 +6895,10 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6511,6 +6955,10 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6567,6 +7015,10 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6623,6 +7075,10 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6679,6 +7135,10 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6735,6 +7195,10 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6791,6 +7255,10 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6847,6 +7315,10 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6901,6 +7373,10 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6957,6 +7433,10 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7013,6 +7493,10 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7069,6 +7553,10 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7125,6 +7613,10 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7181,6 +7673,10 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7237,6 +7733,10 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7293,6 +7793,10 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7349,6 +7853,10 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7405,6 +7913,10 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7461,6 +7973,10 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7517,6 +8033,10 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7573,6 +8093,10 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7629,6 +8153,10 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7685,6 +8213,10 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7741,6 +8273,10 @@
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7797,6 +8333,10 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7853,6 +8393,10 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7907,6 +8451,10 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7963,6 +8511,10 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8019,6 +8571,10 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8073,6 +8629,10 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8129,6 +8689,10 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8185,6 +8749,10 @@
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8241,6 +8809,10 @@
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8297,6 +8869,10 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8353,6 +8929,10 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8409,6 +8989,10 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8465,6 +9049,10 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8521,6 +9109,10 @@
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8577,6 +9169,10 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8633,6 +9229,10 @@
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8689,6 +9289,10 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8745,6 +9349,10 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8801,6 +9409,10 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8855,6 +9467,10 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8911,6 +9527,10 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8967,6 +9587,10 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9023,6 +9647,10 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9077,6 +9705,10 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9133,6 +9765,10 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9189,6 +9825,10 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9233,6 +9873,10 @@
       </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9277,6 +9921,10 @@
       <c r="R158" t="n">
         <v>0.41</v>
       </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9325,6 +9973,10 @@
       <c r="R159" t="n">
         <v>0.276</v>
       </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9373,6 +10025,10 @@
       <c r="R160" t="n">
         <v>0.438</v>
       </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9421,6 +10077,10 @@
       <c r="R161" t="n">
         <v>0.502</v>
       </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9469,6 +10129,10 @@
       <c r="R162" t="n">
         <v>0.536</v>
       </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9517,6 +10181,10 @@
       <c r="R163" t="n">
         <v>0.391</v>
       </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9565,6 +10233,10 @@
       <c r="R164" t="n">
         <v>0.528</v>
       </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9609,6 +10281,10 @@
       </c>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9657,6 +10333,10 @@
       <c r="R166" t="n">
         <v>0.417</v>
       </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9705,6 +10385,10 @@
       <c r="R167" t="n">
         <v>0.296</v>
       </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9753,6 +10437,10 @@
       <c r="R168" t="n">
         <v>0.5580000000000001</v>
       </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9801,6 +10489,10 @@
       <c r="R169" t="n">
         <v>0.591</v>
       </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9849,6 +10541,10 @@
       <c r="R170" t="n">
         <v>0.579</v>
       </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9897,6 +10593,10 @@
       <c r="R171" t="n">
         <v>0.59</v>
       </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9945,6 +10645,10 @@
       <c r="R172" t="n">
         <v>0.5620000000000001</v>
       </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9993,6 +10697,10 @@
       <c r="R173" t="n">
         <v>0.586</v>
       </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10041,6 +10749,10 @@
       <c r="R174" t="n">
         <v>0.511</v>
       </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10089,6 +10801,10 @@
       <c r="R175" t="n">
         <v>0.582</v>
       </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10137,6 +10853,10 @@
       <c r="R176" t="n">
         <v>0.505</v>
       </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10185,6 +10905,10 @@
       <c r="R177" t="n">
         <v>0.505</v>
       </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10233,6 +10957,10 @@
       <c r="R178" t="n">
         <v>0.582</v>
       </c>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10281,6 +11009,10 @@
       <c r="R179" t="n">
         <v>0.397</v>
       </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10329,6 +11061,10 @@
       <c r="R180" t="n">
         <v>0.521</v>
       </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10377,6 +11113,10 @@
       <c r="R181" t="n">
         <v>0.796</v>
       </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10425,6 +11165,10 @@
       <c r="R182" t="n">
         <v>0.327</v>
       </c>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10473,6 +11217,10 @@
       <c r="R183" t="n">
         <v>0.485</v>
       </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10521,6 +11269,10 @@
       <c r="R184" t="n">
         <v>0.554</v>
       </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10569,6 +11321,10 @@
       <c r="R185" t="n">
         <v>0.593</v>
       </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10613,6 +11369,1554 @@
       </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>631</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46147.93953240741</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>630</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46147.30555625</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>628</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46142.28767704861</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V189" t="n">
+        <v>0.517</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>627</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46141.8099630787</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V190" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>626</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46141.80929525463</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="V191" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>625</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46141.80901473379</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>624</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>46141.23518032407</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0.247</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>622</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46139.95462491898</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="V194" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>621</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>46138.80638715278</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>620</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>46138.80605790509</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V196" t="n">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>619</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>46137.77938425926</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="V197" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>618</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>46137.77907341435</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="V198" t="n">
+        <v>0.476</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>616</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>46136.76098680556</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="V199" t="n">
+        <v>0.472</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>615</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>46136.61830679398</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="V200" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>614</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46135.94000211806</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="V201" t="n">
+        <v>0.596</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>612</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46135.62944042824</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="V202" t="n">
+        <v>0.491</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>611</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46134.93859571759</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="U203" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="V203" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>609</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>46134.62234394676</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="V204" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>608</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>46133.96539930555</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0.596</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>606</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>46133.64381924769</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V206" t="n">
+        <v>0.489</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>605</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>46132.80456443287</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V207" t="n">
+        <v>0.493</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>604</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>46132.61948059028</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="V208" t="n">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>603</v>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>46130.78272415509</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>601</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>46130.64483912037</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0.584</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>600</v>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>46130.2331397801</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>598</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>46129.68070162037</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="T212" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="V212" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>597</v>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>46128.61726315972</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="T213" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>596</v>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46127.95040393519</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="T214" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V214" t="n">
+        <v>0.592</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>594</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46127.64660887732</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.491</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-06 15:26:36</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250B-E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>593</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46126.80916261574</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V216"/>
+  <dimension ref="A1:Z246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +541,26 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>OP250B-P2-TAMÑ-MAX-PART-CONT - TAMAÑO MÁXIMO DE PARTÍCULA CONTAMINANTE</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 6</t>
         </is>
       </c>
     </row>
@@ -603,6 +623,10 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -663,6 +687,10 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -723,6 +751,10 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -783,6 +815,10 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -843,6 +879,10 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -903,6 +943,10 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -963,6 +1007,10 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1023,6 +1071,10 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1083,6 +1135,10 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,6 +1199,10 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1203,6 +1263,10 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1263,6 +1327,10 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1323,6 +1391,10 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1383,6 +1455,10 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1443,6 +1519,10 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1503,6 +1583,10 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1563,6 +1647,10 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1623,6 +1711,10 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1683,6 +1775,10 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1743,6 +1839,10 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1803,6 +1903,10 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1863,6 +1967,10 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1923,6 +2031,10 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1983,6 +2095,10 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2043,6 +2159,10 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2103,6 +2223,10 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2163,6 +2287,10 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2223,6 +2351,10 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2283,6 +2415,10 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2343,6 +2479,10 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2403,6 +2543,10 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2463,6 +2607,10 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2523,6 +2671,10 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2583,6 +2735,10 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2643,6 +2799,10 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2703,6 +2863,10 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2763,6 +2927,10 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2823,6 +2991,10 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2883,6 +3055,10 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2943,6 +3119,10 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3003,6 +3183,10 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3063,6 +3247,10 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3123,6 +3311,10 @@
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3183,6 +3375,10 @@
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3241,6 +3437,10 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3301,6 +3501,10 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3361,6 +3565,10 @@
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3421,6 +3629,10 @@
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3481,6 +3693,10 @@
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3541,6 +3757,10 @@
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3601,6 +3821,10 @@
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3661,6 +3885,10 @@
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3721,6 +3949,10 @@
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3781,6 +4013,10 @@
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3841,6 +4077,10 @@
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3901,6 +4141,10 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3961,6 +4205,10 @@
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4021,6 +4269,10 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4081,6 +4333,10 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4141,6 +4397,10 @@
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4201,6 +4461,10 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4261,6 +4525,10 @@
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4321,6 +4589,10 @@
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4381,6 +4653,10 @@
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4441,6 +4717,10 @@
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4501,6 +4781,10 @@
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4561,6 +4845,10 @@
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4621,6 +4909,10 @@
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4681,6 +4973,10 @@
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4741,6 +5037,10 @@
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4801,6 +5101,10 @@
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4861,6 +5165,10 @@
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4921,6 +5229,10 @@
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4981,6 +5293,10 @@
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5041,6 +5357,10 @@
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5101,6 +5421,10 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5161,6 +5485,10 @@
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5221,6 +5549,10 @@
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5281,6 +5613,10 @@
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5341,6 +5677,10 @@
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5401,6 +5741,10 @@
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5461,6 +5805,10 @@
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5521,6 +5869,10 @@
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5581,6 +5933,10 @@
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5641,6 +5997,10 @@
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5701,6 +6061,10 @@
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5761,6 +6125,10 @@
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5821,6 +6189,10 @@
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5881,6 +6253,10 @@
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5941,6 +6317,10 @@
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6001,6 +6381,10 @@
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6061,6 +6445,10 @@
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6119,6 +6507,10 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6179,6 +6571,10 @@
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6239,6 +6635,10 @@
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6299,6 +6699,10 @@
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6359,6 +6763,10 @@
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6419,6 +6827,10 @@
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6479,6 +6891,10 @@
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6539,6 +6955,10 @@
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6599,6 +7019,10 @@
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6659,6 +7083,10 @@
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6719,6 +7147,10 @@
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6779,6 +7211,10 @@
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6839,6 +7275,10 @@
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6899,6 +7339,10 @@
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6959,6 +7403,10 @@
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7019,6 +7467,10 @@
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7079,6 +7531,10 @@
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7139,6 +7595,10 @@
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7199,6 +7659,10 @@
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7259,6 +7723,10 @@
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7319,6 +7787,10 @@
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7377,6 +7849,10 @@
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7437,6 +7913,10 @@
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7497,6 +7977,10 @@
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7557,6 +8041,10 @@
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7617,6 +8105,10 @@
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7677,6 +8169,10 @@
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7737,6 +8233,10 @@
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7797,6 +8297,10 @@
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7857,6 +8361,10 @@
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7917,6 +8425,10 @@
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7977,6 +8489,10 @@
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8037,6 +8553,10 @@
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8097,6 +8617,10 @@
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8157,6 +8681,10 @@
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8217,6 +8745,10 @@
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8277,6 +8809,10 @@
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8337,6 +8873,10 @@
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8397,6 +8937,10 @@
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8455,6 +8999,10 @@
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8515,6 +9063,10 @@
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
+      <c r="W134" t="inlineStr"/>
+      <c r="X134" t="inlineStr"/>
+      <c r="Y134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8575,6 +9127,10 @@
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8633,6 +9189,10 @@
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8693,6 +9253,10 @@
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8753,6 +9317,10 @@
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8813,6 +9381,10 @@
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8873,6 +9445,10 @@
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8933,6 +9509,10 @@
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8993,6 +9573,10 @@
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9053,6 +9637,10 @@
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr"/>
+      <c r="Z143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9113,6 +9701,10 @@
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9173,6 +9765,10 @@
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9233,6 +9829,10 @@
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr"/>
+      <c r="Z146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9293,6 +9893,10 @@
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9353,6 +9957,10 @@
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr"/>
+      <c r="Y148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9413,6 +10021,10 @@
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr"/>
+      <c r="Y149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9471,6 +10083,10 @@
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr"/>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9531,6 +10147,10 @@
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr"/>
+      <c r="Y151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9591,6 +10211,10 @@
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
+      <c r="Y152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9651,6 +10275,10 @@
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9709,6 +10337,10 @@
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9769,6 +10401,10 @@
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr"/>
+      <c r="Y155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9829,6 +10465,10 @@
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
+      <c r="W156" t="inlineStr"/>
+      <c r="X156" t="inlineStr"/>
+      <c r="Y156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9877,6 +10517,10 @@
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9925,6 +10569,10 @@
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="inlineStr"/>
+      <c r="Y158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9977,6 +10625,10 @@
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="inlineStr"/>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10029,6 +10681,10 @@
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr"/>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10081,6 +10737,10 @@
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
+      <c r="W161" t="inlineStr"/>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10133,6 +10793,10 @@
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10185,6 +10849,10 @@
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
+      <c r="W163" t="inlineStr"/>
+      <c r="X163" t="inlineStr"/>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10237,6 +10905,10 @@
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
+      <c r="W164" t="inlineStr"/>
+      <c r="X164" t="inlineStr"/>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10285,6 +10957,10 @@
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
+      <c r="W165" t="inlineStr"/>
+      <c r="X165" t="inlineStr"/>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10337,6 +11013,10 @@
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
+      <c r="W166" t="inlineStr"/>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10389,6 +11069,10 @@
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
+      <c r="W167" t="inlineStr"/>
+      <c r="X167" t="inlineStr"/>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10441,6 +11125,10 @@
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr"/>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10493,6 +11181,10 @@
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10545,6 +11237,10 @@
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
+      <c r="W170" t="inlineStr"/>
+      <c r="X170" t="inlineStr"/>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10597,6 +11293,10 @@
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10649,6 +11349,10 @@
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
+      <c r="W172" t="inlineStr"/>
+      <c r="X172" t="inlineStr"/>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10701,6 +11405,10 @@
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
+      <c r="W173" t="inlineStr"/>
+      <c r="X173" t="inlineStr"/>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10753,6 +11461,10 @@
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10805,6 +11517,10 @@
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10857,6 +11573,10 @@
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10909,6 +11629,10 @@
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10961,6 +11685,10 @@
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11013,6 +11741,10 @@
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr"/>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr"/>
+      <c r="Z179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11065,6 +11797,10 @@
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11117,6 +11853,10 @@
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr"/>
+      <c r="Z181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11169,6 +11909,10 @@
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11221,6 +11965,10 @@
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11273,6 +12021,10 @@
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11325,6 +12077,10 @@
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11373,6 +12129,10 @@
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11421,6 +12181,10 @@
       </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11469,6 +12233,10 @@
       <c r="V188" t="n">
         <v>0.273</v>
       </c>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11521,6 +12289,10 @@
       <c r="V189" t="n">
         <v>0.517</v>
       </c>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11573,6 +12345,10 @@
       <c r="V190" t="n">
         <v>0.286</v>
       </c>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11625,6 +12401,10 @@
       <c r="V191" t="n">
         <v>0.58</v>
       </c>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11677,6 +12457,10 @@
       <c r="V192" t="n">
         <v>0.59</v>
       </c>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11729,6 +12513,10 @@
       <c r="V193" t="n">
         <v>0.247</v>
       </c>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11781,6 +12569,10 @@
       <c r="V194" t="n">
         <v>0.5649999999999999</v>
       </c>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11829,6 +12621,10 @@
       </c>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11881,6 +12677,10 @@
       <c r="V196" t="n">
         <v>0.311</v>
       </c>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11933,6 +12733,10 @@
       <c r="V197" t="n">
         <v>0.43</v>
       </c>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11985,6 +12789,10 @@
       <c r="V198" t="n">
         <v>0.476</v>
       </c>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12037,6 +12845,10 @@
       <c r="V199" t="n">
         <v>0.472</v>
       </c>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12089,6 +12901,10 @@
       <c r="V200" t="n">
         <v>0.531</v>
       </c>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12141,6 +12957,10 @@
       <c r="V201" t="n">
         <v>0.596</v>
       </c>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12193,6 +13013,10 @@
       <c r="V202" t="n">
         <v>0.491</v>
       </c>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12245,6 +13069,10 @@
       <c r="V203" t="n">
         <v>0.59</v>
       </c>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12297,6 +13125,10 @@
       <c r="V204" t="n">
         <v>0.573</v>
       </c>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12349,6 +13181,10 @@
       <c r="V205" t="n">
         <v>0.596</v>
       </c>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12401,6 +13237,10 @@
       <c r="V206" t="n">
         <v>0.489</v>
       </c>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12453,6 +13293,10 @@
       <c r="V207" t="n">
         <v>0.493</v>
       </c>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12505,6 +13349,10 @@
       <c r="V208" t="n">
         <v>0.536</v>
       </c>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12557,6 +13405,10 @@
       <c r="V209" t="n">
         <v>0.364</v>
       </c>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12609,6 +13461,10 @@
       <c r="V210" t="n">
         <v>0.584</v>
       </c>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12661,6 +13517,10 @@
       <c r="V211" t="n">
         <v>0.914</v>
       </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12713,6 +13573,10 @@
       <c r="V212" t="n">
         <v>0.5659999999999999</v>
       </c>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12765,6 +13629,10 @@
       <c r="V213" t="n">
         <v>0.574</v>
       </c>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12817,6 +13685,10 @@
       <c r="V214" t="n">
         <v>0.592</v>
       </c>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12869,6 +13741,10 @@
       <c r="V215" t="n">
         <v>2.491</v>
       </c>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12917,6 +13793,1330 @@
       </c>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>629</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46147.93938163194</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>628</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46147.30529413195</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>626</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46142.28737384259</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>625</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46141.80884197917</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
+      <c r="W220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr"/>
+      <c r="Z220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>624</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46141.80829452546</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr"/>
+      <c r="Z221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>623</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46141.80793359954</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="inlineStr"/>
+      <c r="Z222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>622</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46141.23464876157</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
+      <c r="W223" t="inlineStr"/>
+      <c r="X223" t="inlineStr"/>
+      <c r="Y223" t="inlineStr"/>
+      <c r="Z223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>621</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46139.95437916667</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr"/>
+      <c r="Z224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>620</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46138.80580034723</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+      <c r="W225" t="inlineStr"/>
+      <c r="X225" t="inlineStr"/>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>619</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46138.80544158565</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+      <c r="W226" t="inlineStr"/>
+      <c r="X226" t="inlineStr"/>
+      <c r="Y226" t="inlineStr"/>
+      <c r="Z226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>618</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46137.7788162037</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
+      <c r="W227" t="inlineStr"/>
+      <c r="X227" t="inlineStr"/>
+      <c r="Y227" t="inlineStr"/>
+      <c r="Z227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>617</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46137.77851038195</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
+      <c r="W228" t="inlineStr"/>
+      <c r="X228" t="inlineStr"/>
+      <c r="Y228" t="inlineStr"/>
+      <c r="Z228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>615</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46136.76072306713</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>614</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46136.61789722222</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>613</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46135.93963109954</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="inlineStr"/>
+      <c r="Z231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>611</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46135.62895987269</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="inlineStr"/>
+      <c r="Y232" t="inlineStr"/>
+      <c r="Z232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>610</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46134.93833425926</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
+      <c r="W233" t="inlineStr"/>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr"/>
+      <c r="Z233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>608</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46134.62196600695</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr"/>
+      <c r="Z234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>607</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46133.96499421296</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
+      <c r="W235" t="inlineStr"/>
+      <c r="X235" t="inlineStr"/>
+      <c r="Y235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>605</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46133.64347612268</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr"/>
+      <c r="W236" t="inlineStr"/>
+      <c r="X236" t="inlineStr"/>
+      <c r="Y236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>604</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46132.80430100695</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr"/>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="inlineStr"/>
+      <c r="Y237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>603</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46132.61887288195</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr"/>
+      <c r="W238" t="inlineStr"/>
+      <c r="X238" t="inlineStr"/>
+      <c r="Y238" t="inlineStr"/>
+      <c r="Z238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>602</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46130.78241103009</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="inlineStr"/>
+      <c r="W239" t="inlineStr"/>
+      <c r="X239" t="inlineStr"/>
+      <c r="Y239" t="inlineStr"/>
+      <c r="Z239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>600</v>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>46130.64431554398</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr"/>
+      <c r="V240" t="inlineStr"/>
+      <c r="W240" t="inlineStr"/>
+      <c r="X240" t="inlineStr"/>
+      <c r="Y240" t="inlineStr"/>
+      <c r="Z240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>599</v>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>46130.23244186342</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr"/>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="inlineStr"/>
+      <c r="W241" t="inlineStr"/>
+      <c r="X241" t="inlineStr"/>
+      <c r="Y241" t="inlineStr"/>
+      <c r="Z241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>597</v>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>46129.68032268518</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr"/>
+      <c r="U242" t="inlineStr"/>
+      <c r="V242" t="inlineStr"/>
+      <c r="W242" t="inlineStr"/>
+      <c r="X242" t="inlineStr"/>
+      <c r="Y242" t="inlineStr"/>
+      <c r="Z242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>596</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46128.6166440625</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr"/>
+      <c r="W243" t="inlineStr"/>
+      <c r="X243" t="inlineStr"/>
+      <c r="Y243" t="inlineStr"/>
+      <c r="Z243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>595</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>46127.9500162037</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr"/>
+      <c r="W244" t="inlineStr"/>
+      <c r="X244" t="inlineStr"/>
+      <c r="Y244" t="inlineStr"/>
+      <c r="Z244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>593</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>46127.64626924769</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr"/>
+      <c r="W245" t="inlineStr"/>
+      <c r="X245" t="inlineStr"/>
+      <c r="Y245" t="inlineStr"/>
+      <c r="Z245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:03:24</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Línea 2 (Stellantis)</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>592</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>46126.80897890047</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr"/>
+      <c r="W246" t="inlineStr"/>
+      <c r="X246" t="inlineStr"/>
+      <c r="Y246" t="inlineStr"/>
+      <c r="Z246" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z246"/>
+  <dimension ref="A1:Z216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13798,1326 +13798,6 @@
       <c r="Y216" t="inlineStr"/>
       <c r="Z216" t="inlineStr"/>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>629</v>
-      </c>
-      <c r="E217" s="2" t="n">
-        <v>46147.93938163194</v>
-      </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
-      <c r="W217" t="inlineStr"/>
-      <c r="X217" t="inlineStr"/>
-      <c r="Y217" t="inlineStr"/>
-      <c r="Z217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>628</v>
-      </c>
-      <c r="E218" s="2" t="n">
-        <v>46147.30529413195</v>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
-      <c r="U218" t="inlineStr"/>
-      <c r="V218" t="inlineStr"/>
-      <c r="W218" t="inlineStr"/>
-      <c r="X218" t="inlineStr"/>
-      <c r="Y218" t="inlineStr"/>
-      <c r="Z218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>626</v>
-      </c>
-      <c r="E219" s="2" t="n">
-        <v>46142.28737384259</v>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
-      <c r="V219" t="inlineStr"/>
-      <c r="W219" t="inlineStr"/>
-      <c r="X219" t="inlineStr"/>
-      <c r="Y219" t="inlineStr"/>
-      <c r="Z219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>625</v>
-      </c>
-      <c r="E220" s="2" t="n">
-        <v>46141.80884197917</v>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
-      <c r="T220" t="inlineStr"/>
-      <c r="U220" t="inlineStr"/>
-      <c r="V220" t="inlineStr"/>
-      <c r="W220" t="inlineStr"/>
-      <c r="X220" t="inlineStr"/>
-      <c r="Y220" t="inlineStr"/>
-      <c r="Z220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>624</v>
-      </c>
-      <c r="E221" s="2" t="n">
-        <v>46141.80829452546</v>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
-      <c r="U221" t="inlineStr"/>
-      <c r="V221" t="inlineStr"/>
-      <c r="W221" t="inlineStr"/>
-      <c r="X221" t="inlineStr"/>
-      <c r="Y221" t="inlineStr"/>
-      <c r="Z221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>623</v>
-      </c>
-      <c r="E222" s="2" t="n">
-        <v>46141.80793359954</v>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
-      <c r="W222" t="inlineStr"/>
-      <c r="X222" t="inlineStr"/>
-      <c r="Y222" t="inlineStr"/>
-      <c r="Z222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>622</v>
-      </c>
-      <c r="E223" s="2" t="n">
-        <v>46141.23464876157</v>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
-      <c r="V223" t="inlineStr"/>
-      <c r="W223" t="inlineStr"/>
-      <c r="X223" t="inlineStr"/>
-      <c r="Y223" t="inlineStr"/>
-      <c r="Z223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>621</v>
-      </c>
-      <c r="E224" s="2" t="n">
-        <v>46139.95437916667</v>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
-      <c r="U224" t="inlineStr"/>
-      <c r="V224" t="inlineStr"/>
-      <c r="W224" t="inlineStr"/>
-      <c r="X224" t="inlineStr"/>
-      <c r="Y224" t="inlineStr"/>
-      <c r="Z224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>620</v>
-      </c>
-      <c r="E225" s="2" t="n">
-        <v>46138.80580034723</v>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
-      <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
-      <c r="W225" t="inlineStr"/>
-      <c r="X225" t="inlineStr"/>
-      <c r="Y225" t="inlineStr"/>
-      <c r="Z225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>619</v>
-      </c>
-      <c r="E226" s="2" t="n">
-        <v>46138.80544158565</v>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
-      <c r="T226" t="inlineStr"/>
-      <c r="U226" t="inlineStr"/>
-      <c r="V226" t="inlineStr"/>
-      <c r="W226" t="inlineStr"/>
-      <c r="X226" t="inlineStr"/>
-      <c r="Y226" t="inlineStr"/>
-      <c r="Z226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>618</v>
-      </c>
-      <c r="E227" s="2" t="n">
-        <v>46137.7788162037</v>
-      </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
-      <c r="T227" t="inlineStr"/>
-      <c r="U227" t="inlineStr"/>
-      <c r="V227" t="inlineStr"/>
-      <c r="W227" t="inlineStr"/>
-      <c r="X227" t="inlineStr"/>
-      <c r="Y227" t="inlineStr"/>
-      <c r="Z227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>617</v>
-      </c>
-      <c r="E228" s="2" t="n">
-        <v>46137.77851038195</v>
-      </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
-      <c r="W228" t="inlineStr"/>
-      <c r="X228" t="inlineStr"/>
-      <c r="Y228" t="inlineStr"/>
-      <c r="Z228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>615</v>
-      </c>
-      <c r="E229" s="2" t="n">
-        <v>46136.76072306713</v>
-      </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
-      <c r="T229" t="inlineStr"/>
-      <c r="U229" t="inlineStr"/>
-      <c r="V229" t="inlineStr"/>
-      <c r="W229" t="inlineStr"/>
-      <c r="X229" t="inlineStr"/>
-      <c r="Y229" t="inlineStr"/>
-      <c r="Z229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>614</v>
-      </c>
-      <c r="E230" s="2" t="n">
-        <v>46136.61789722222</v>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
-      <c r="T230" t="inlineStr"/>
-      <c r="U230" t="inlineStr"/>
-      <c r="V230" t="inlineStr"/>
-      <c r="W230" t="inlineStr"/>
-      <c r="X230" t="inlineStr"/>
-      <c r="Y230" t="inlineStr"/>
-      <c r="Z230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>613</v>
-      </c>
-      <c r="E231" s="2" t="n">
-        <v>46135.93963109954</v>
-      </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr"/>
-      <c r="W231" t="inlineStr"/>
-      <c r="X231" t="inlineStr"/>
-      <c r="Y231" t="inlineStr"/>
-      <c r="Z231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>611</v>
-      </c>
-      <c r="E232" s="2" t="n">
-        <v>46135.62895987269</v>
-      </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
-      <c r="T232" t="inlineStr"/>
-      <c r="U232" t="inlineStr"/>
-      <c r="V232" t="inlineStr"/>
-      <c r="W232" t="inlineStr"/>
-      <c r="X232" t="inlineStr"/>
-      <c r="Y232" t="inlineStr"/>
-      <c r="Z232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>610</v>
-      </c>
-      <c r="E233" s="2" t="n">
-        <v>46134.93833425926</v>
-      </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
-      <c r="T233" t="inlineStr"/>
-      <c r="U233" t="inlineStr"/>
-      <c r="V233" t="inlineStr"/>
-      <c r="W233" t="inlineStr"/>
-      <c r="X233" t="inlineStr"/>
-      <c r="Y233" t="inlineStr"/>
-      <c r="Z233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>608</v>
-      </c>
-      <c r="E234" s="2" t="n">
-        <v>46134.62196600695</v>
-      </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr"/>
-      <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
-      <c r="W234" t="inlineStr"/>
-      <c r="X234" t="inlineStr"/>
-      <c r="Y234" t="inlineStr"/>
-      <c r="Z234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>607</v>
-      </c>
-      <c r="E235" s="2" t="n">
-        <v>46133.96499421296</v>
-      </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
-      <c r="T235" t="inlineStr"/>
-      <c r="U235" t="inlineStr"/>
-      <c r="V235" t="inlineStr"/>
-      <c r="W235" t="inlineStr"/>
-      <c r="X235" t="inlineStr"/>
-      <c r="Y235" t="inlineStr"/>
-      <c r="Z235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>605</v>
-      </c>
-      <c r="E236" s="2" t="n">
-        <v>46133.64347612268</v>
-      </c>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
-      <c r="T236" t="inlineStr"/>
-      <c r="U236" t="inlineStr"/>
-      <c r="V236" t="inlineStr"/>
-      <c r="W236" t="inlineStr"/>
-      <c r="X236" t="inlineStr"/>
-      <c r="Y236" t="inlineStr"/>
-      <c r="Z236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>604</v>
-      </c>
-      <c r="E237" s="2" t="n">
-        <v>46132.80430100695</v>
-      </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr"/>
-      <c r="S237" t="inlineStr"/>
-      <c r="T237" t="inlineStr"/>
-      <c r="U237" t="inlineStr"/>
-      <c r="V237" t="inlineStr"/>
-      <c r="W237" t="inlineStr"/>
-      <c r="X237" t="inlineStr"/>
-      <c r="Y237" t="inlineStr"/>
-      <c r="Z237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>603</v>
-      </c>
-      <c r="E238" s="2" t="n">
-        <v>46132.61887288195</v>
-      </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
-      <c r="S238" t="inlineStr"/>
-      <c r="T238" t="inlineStr"/>
-      <c r="U238" t="inlineStr"/>
-      <c r="V238" t="inlineStr"/>
-      <c r="W238" t="inlineStr"/>
-      <c r="X238" t="inlineStr"/>
-      <c r="Y238" t="inlineStr"/>
-      <c r="Z238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>602</v>
-      </c>
-      <c r="E239" s="2" t="n">
-        <v>46130.78241103009</v>
-      </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
-      <c r="S239" t="inlineStr"/>
-      <c r="T239" t="inlineStr"/>
-      <c r="U239" t="inlineStr"/>
-      <c r="V239" t="inlineStr"/>
-      <c r="W239" t="inlineStr"/>
-      <c r="X239" t="inlineStr"/>
-      <c r="Y239" t="inlineStr"/>
-      <c r="Z239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>600</v>
-      </c>
-      <c r="E240" s="2" t="n">
-        <v>46130.64431554398</v>
-      </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
-      <c r="S240" t="inlineStr"/>
-      <c r="T240" t="inlineStr"/>
-      <c r="U240" t="inlineStr"/>
-      <c r="V240" t="inlineStr"/>
-      <c r="W240" t="inlineStr"/>
-      <c r="X240" t="inlineStr"/>
-      <c r="Y240" t="inlineStr"/>
-      <c r="Z240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>599</v>
-      </c>
-      <c r="E241" s="2" t="n">
-        <v>46130.23244186342</v>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
-      <c r="T241" t="inlineStr"/>
-      <c r="U241" t="inlineStr"/>
-      <c r="V241" t="inlineStr"/>
-      <c r="W241" t="inlineStr"/>
-      <c r="X241" t="inlineStr"/>
-      <c r="Y241" t="inlineStr"/>
-      <c r="Z241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>597</v>
-      </c>
-      <c r="E242" s="2" t="n">
-        <v>46129.68032268518</v>
-      </c>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
-      <c r="T242" t="inlineStr"/>
-      <c r="U242" t="inlineStr"/>
-      <c r="V242" t="inlineStr"/>
-      <c r="W242" t="inlineStr"/>
-      <c r="X242" t="inlineStr"/>
-      <c r="Y242" t="inlineStr"/>
-      <c r="Z242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>596</v>
-      </c>
-      <c r="E243" s="2" t="n">
-        <v>46128.6166440625</v>
-      </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr"/>
-      <c r="U243" t="inlineStr"/>
-      <c r="V243" t="inlineStr"/>
-      <c r="W243" t="inlineStr"/>
-      <c r="X243" t="inlineStr"/>
-      <c r="Y243" t="inlineStr"/>
-      <c r="Z243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>595</v>
-      </c>
-      <c r="E244" s="2" t="n">
-        <v>46127.9500162037</v>
-      </c>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
-      <c r="T244" t="inlineStr"/>
-      <c r="U244" t="inlineStr"/>
-      <c r="V244" t="inlineStr"/>
-      <c r="W244" t="inlineStr"/>
-      <c r="X244" t="inlineStr"/>
-      <c r="Y244" t="inlineStr"/>
-      <c r="Z244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>593</v>
-      </c>
-      <c r="E245" s="2" t="n">
-        <v>46127.64626924769</v>
-      </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
-      <c r="T245" t="inlineStr"/>
-      <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
-      <c r="W245" t="inlineStr"/>
-      <c r="X245" t="inlineStr"/>
-      <c r="Y245" t="inlineStr"/>
-      <c r="Z245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-05-06 16:03:24</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Sedimts-Op.250A- E1/E2 - Big Gas</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Línea 2 (Stellantis)</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>592</v>
-      </c>
-      <c r="E246" s="2" t="n">
-        <v>46126.80897890047</v>
-      </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
-      <c r="R246" t="inlineStr"/>
-      <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr"/>
-      <c r="U246" t="inlineStr"/>
-      <c r="V246" t="inlineStr"/>
-      <c r="W246" t="inlineStr"/>
-      <c r="X246" t="inlineStr"/>
-      <c r="Y246" t="inlineStr"/>
-      <c r="Z246" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z216"/>
+  <dimension ref="A1:Z217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13798,6 +13798,70 @@
       <c r="Y216" t="inlineStr"/>
       <c r="Z216" t="inlineStr"/>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:15:47</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>52</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46149.29242878472</v>
+      </c>
+      <c r="F217" t="n">
+        <v>82066</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H217" t="n">
+        <v>21</v>
+      </c>
+      <c r="I217" t="n">
+        <v>14</v>
+      </c>
+      <c r="J217" t="n">
+        <v>14</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z217"/>
+  <dimension ref="A1:Z218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13862,6 +13862,70 @@
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:17:13</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>38</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46149.29267017361</v>
+      </c>
+      <c r="F218" t="n">
+        <v>82079</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H218" t="n">
+        <v>22</v>
+      </c>
+      <c r="I218" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" t="n">
+        <v>17</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z218"/>
+  <dimension ref="A1:Z220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13926,6 +13926,134 @@
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="inlineStr"/>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:18:39</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>32</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46149.2929352662</v>
+      </c>
+      <c r="F219" t="n">
+        <v>80587</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H219" t="n">
+        <v>54</v>
+      </c>
+      <c r="I219" t="n">
+        <v>10</v>
+      </c>
+      <c r="J219" t="n">
+        <v>24</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:18:39</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>31</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46148.94305871527</v>
+      </c>
+      <c r="F220" t="n">
+        <v>81185</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H220" t="n">
+        <v>35</v>
+      </c>
+      <c r="I220" t="n">
+        <v>7</v>
+      </c>
+      <c r="J220" t="n">
+        <v>24</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
+      <c r="W220" t="inlineStr"/>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr"/>
+      <c r="Z220" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z220"/>
+  <dimension ref="A1:Z222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14054,6 +14054,134 @@
       <c r="Y220" t="inlineStr"/>
       <c r="Z220" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:20:02</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>30</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46149.29319178241</v>
+      </c>
+      <c r="F221" t="n">
+        <v>81203</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H221" t="n">
+        <v>70</v>
+      </c>
+      <c r="I221" t="n">
+        <v>6</v>
+      </c>
+      <c r="J221" t="n">
+        <v>20</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr"/>
+      <c r="Z221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:20:02</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>29</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46148.94345995371</v>
+      </c>
+      <c r="F222" t="n">
+        <v>81288</v>
+      </c>
+      <c r="G222" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H222" t="n">
+        <v>23</v>
+      </c>
+      <c r="I222" t="n">
+        <v>3</v>
+      </c>
+      <c r="J222" t="n">
+        <v>22</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>3</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="inlineStr"/>
+      <c r="Z222" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z222"/>
+  <dimension ref="A1:Z224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14182,6 +14182,134 @@
       <c r="Y222" t="inlineStr"/>
       <c r="Z222" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:46:37</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>54</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46149.64881855324</v>
+      </c>
+      <c r="F223" t="n">
+        <v>81406</v>
+      </c>
+      <c r="G223" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H223" t="n">
+        <v>24</v>
+      </c>
+      <c r="I223" t="n">
+        <v>4</v>
+      </c>
+      <c r="J223" t="n">
+        <v>9</v>
+      </c>
+      <c r="K223" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
+      <c r="W223" t="inlineStr"/>
+      <c r="X223" t="inlineStr"/>
+      <c r="Y223" t="inlineStr"/>
+      <c r="Z223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:46:37</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>53</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46149.64855517361</v>
+      </c>
+      <c r="F224" t="n">
+        <v>80971</v>
+      </c>
+      <c r="G224" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H224" t="n">
+        <v>11</v>
+      </c>
+      <c r="I224" t="n">
+        <v>8</v>
+      </c>
+      <c r="J224" t="n">
+        <v>15</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr"/>
+      <c r="Z224" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z224"/>
+  <dimension ref="A1:Z225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14310,6 +14310,70 @@
       <c r="Y224" t="inlineStr"/>
       <c r="Z224" t="inlineStr"/>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:47:57</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>39</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46149.64925524306</v>
+      </c>
+      <c r="F225" t="n">
+        <v>81406</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H225" t="n">
+        <v>24</v>
+      </c>
+      <c r="I225" t="n">
+        <v>4</v>
+      </c>
+      <c r="J225" t="n">
+        <v>9</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+      <c r="W225" t="inlineStr"/>
+      <c r="X225" t="inlineStr"/>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z225"/>
+  <dimension ref="A1:Z230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14374,6 +14374,326 @@
       <c r="Y225" t="inlineStr"/>
       <c r="Z225" t="inlineStr"/>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:49:17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>38</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46149.65028792824</v>
+      </c>
+      <c r="F226" t="n">
+        <v>82357</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H226" t="n">
+        <v>81</v>
+      </c>
+      <c r="I226" t="n">
+        <v>8</v>
+      </c>
+      <c r="J226" t="n">
+        <v>21</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+      <c r="W226" t="inlineStr"/>
+      <c r="X226" t="inlineStr"/>
+      <c r="Y226" t="inlineStr"/>
+      <c r="Z226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:49:17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>36</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46149.64294826389</v>
+      </c>
+      <c r="F227" t="n">
+        <v>81978</v>
+      </c>
+      <c r="G227" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H227" t="n">
+        <v>32</v>
+      </c>
+      <c r="I227" t="n">
+        <v>5</v>
+      </c>
+      <c r="J227" t="n">
+        <v>23</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
+      <c r="W227" t="inlineStr"/>
+      <c r="X227" t="inlineStr"/>
+      <c r="Y227" t="inlineStr"/>
+      <c r="Z227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:49:17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>35</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46149.63845813657</v>
+      </c>
+      <c r="F228" t="n">
+        <v>81962</v>
+      </c>
+      <c r="G228" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H228" t="n">
+        <v>28</v>
+      </c>
+      <c r="I228" t="n">
+        <v>12</v>
+      </c>
+      <c r="J228" t="n">
+        <v>18</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
+      <c r="W228" t="inlineStr"/>
+      <c r="X228" t="inlineStr"/>
+      <c r="Y228" t="inlineStr"/>
+      <c r="Z228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:49:17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>34</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46149.63801408565</v>
+      </c>
+      <c r="F229" t="n">
+        <v>81557</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H229" t="n">
+        <v>19</v>
+      </c>
+      <c r="I229" t="n">
+        <v>9</v>
+      </c>
+      <c r="J229" t="n">
+        <v>10</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:49:17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>33</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46149.63615795139</v>
+      </c>
+      <c r="F230" t="n">
+        <v>81553</v>
+      </c>
+      <c r="G230" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H230" t="n">
+        <v>90</v>
+      </c>
+      <c r="I230" t="n">
+        <v>3</v>
+      </c>
+      <c r="J230" t="n">
+        <v>11</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z230"/>
+  <dimension ref="A1:Z233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14694,6 +14694,198 @@
       <c r="Y230" t="inlineStr"/>
       <c r="Z230" t="inlineStr"/>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:50:37</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>34</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>46149.65081956019</v>
+      </c>
+      <c r="F231" t="n">
+        <v>82370</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H231" t="n">
+        <v>114</v>
+      </c>
+      <c r="I231" t="n">
+        <v>12</v>
+      </c>
+      <c r="J231" t="n">
+        <v>28</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="inlineStr"/>
+      <c r="Z231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:50:37</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>32</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>46149.64527488426</v>
+      </c>
+      <c r="F232" t="n">
+        <v>81041</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H232" t="n">
+        <v>103</v>
+      </c>
+      <c r="I232" t="n">
+        <v>26</v>
+      </c>
+      <c r="J232" t="n">
+        <v>11</v>
+      </c>
+      <c r="K232" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="inlineStr"/>
+      <c r="Y232" t="inlineStr"/>
+      <c r="Z232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:50:37</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>31</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>46149.645034375</v>
+      </c>
+      <c r="F233" t="n">
+        <v>80290</v>
+      </c>
+      <c r="G233" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H233" t="n">
+        <v>121</v>
+      </c>
+      <c r="I233" t="n">
+        <v>24</v>
+      </c>
+      <c r="J233" t="n">
+        <v>17</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
+      <c r="W233" t="inlineStr"/>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr"/>
+      <c r="Z233" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z233"/>
+  <dimension ref="A1:Z234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14886,6 +14886,70 @@
       <c r="Y233" t="inlineStr"/>
       <c r="Z233" t="inlineStr"/>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:49:57</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>OP. 190_1</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>3372</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>46150.28511203704</v>
+      </c>
+      <c r="F234" t="n">
+        <v>77284</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H234" t="n">
+        <v>72</v>
+      </c>
+      <c r="I234" t="n">
+        <v>12</v>
+      </c>
+      <c r="J234" t="n">
+        <v>28</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr"/>
+      <c r="Z234" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z234"/>
+  <dimension ref="A1:Z235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14950,6 +14950,70 @@
       <c r="Y234" t="inlineStr"/>
       <c r="Z234" t="inlineStr"/>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:51:19</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>OP. 190_2</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>46150.28551238426</v>
+      </c>
+      <c r="F235" t="n">
+        <v>77376</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H235" t="n">
+        <v>64</v>
+      </c>
+      <c r="I235" t="n">
+        <v>10</v>
+      </c>
+      <c r="J235" t="n">
+        <v>22</v>
+      </c>
+      <c r="K235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
+      <c r="W235" t="inlineStr"/>
+      <c r="X235" t="inlineStr"/>
+      <c r="Y235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z235"/>
+  <dimension ref="A1:Z236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15014,6 +15014,70 @@
       <c r="Y235" t="inlineStr"/>
       <c r="Z235" t="inlineStr"/>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:52:41</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-A1</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>56</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46149.79968541666</v>
+      </c>
+      <c r="F236" t="n">
+        <v>80175</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H236" t="n">
+        <v>51</v>
+      </c>
+      <c r="I236" t="n">
+        <v>13</v>
+      </c>
+      <c r="J236" t="n">
+        <v>17</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr"/>
+      <c r="W236" t="inlineStr"/>
+      <c r="X236" t="inlineStr"/>
+      <c r="Y236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z236"/>
+  <dimension ref="A1:Z237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15078,6 +15078,70 @@
       <c r="Y236" t="inlineStr"/>
       <c r="Z236" t="inlineStr"/>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:54:04</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OP. 190B-SUJINO-B1</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>41</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>46149.80009606481</v>
+      </c>
+      <c r="F237" t="n">
+        <v>79431</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H237" t="n">
+        <v>20</v>
+      </c>
+      <c r="I237" t="n">
+        <v>8</v>
+      </c>
+      <c r="J237" t="n">
+        <v>21</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr"/>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="inlineStr"/>
+      <c r="Y237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z237"/>
+  <dimension ref="A1:Z238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15142,6 +15142,70 @@
       <c r="Y237" t="inlineStr"/>
       <c r="Z237" t="inlineStr"/>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:55:26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-A2</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>40</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46149.99321952547</v>
+      </c>
+      <c r="F238" t="n">
+        <v>77185</v>
+      </c>
+      <c r="G238" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H238" t="n">
+        <v>64</v>
+      </c>
+      <c r="I238" t="n">
+        <v>10</v>
+      </c>
+      <c r="J238" t="n">
+        <v>22</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr"/>
+      <c r="W238" t="inlineStr"/>
+      <c r="X238" t="inlineStr"/>
+      <c r="Y238" t="inlineStr"/>
+      <c r="Z238" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_LECTURAS_LIVE.xlsx
+++ b/BD_LECTURAS_LIVE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z238"/>
+  <dimension ref="A1:Z239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15206,6 +15206,70 @@
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-08 08:56:49</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>OP. 190C-SUJINO-B2</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Línea 6 (GM)</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>37</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46149.9936008912</v>
+      </c>
+      <c r="F239" t="n">
+        <v>77246</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H239" t="n">
+        <v>46</v>
+      </c>
+      <c r="I239" t="n">
+        <v>6</v>
+      </c>
+      <c r="J239" t="n">
+        <v>18</v>
+      </c>
+      <c r="K239" t="n">
+        <v>2</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>3</v>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Oscar Saucedo Mendieta</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="inlineStr"/>
+      <c r="W239" t="inlineStr"/>
+      <c r="X239" t="inlineStr"/>
+      <c r="Y239" t="inlineStr"/>
+      <c r="Z239" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
